--- a/TestKit/Q1/Environment.xlsx
+++ b/TestKit/Q1/Environment.xlsx
@@ -1,283 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\NET\Recorder_NetWorking\WpfUI\Resources\Templates\DotnetNetworking\Question\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1734F499-C41A-4E64-ABE7-48FF16AEE5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Config" sheetId="1" r:id="rId1"/>
-    <sheet name="Action" sheetId="3" r:id="rId2"/>
-    <sheet name="Run" sheetId="4" r:id="rId6"/>
+    <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Action" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Run" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1" fullPrecision="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Environment_Type</t>
-  </si>
-  <si>
-    <t>dotnet</t>
-  </si>
-  <si>
-    <t>Docker_Network</t>
-  </si>
-  <si>
-    <t>auto-grading-network</t>
-  </si>
-  <si>
-    <t>Code_Image_Name</t>
-  </si>
-  <si>
-    <t>fptuxaes/aes-dotnet8:latest</t>
-  </si>
-  <si>
-    <t>Code_Container_Name</t>
-  </si>
-  <si>
-    <t>auto-grading-dotnet-console-app</t>
-  </si>
-  <si>
-    <t>Code_Container_Internal_Port</t>
-  </si>
-  <si>
-    <t>Code_Container_Host_Port</t>
-  </si>
-  <si>
-    <t>App_Type</t>
-  </si>
-  <si>
-    <t>Console</t>
-  </si>
-  <si>
-    <t>Given_Console_Container_Name</t>
-  </si>
-  <si>
-    <t>Given_Console_File</t>
-  </si>
-  <si>
-    <t>Given_Console_Internal_Port</t>
-  </si>
-  <si>
-    <t>Given_Console_Host_Port</t>
-  </si>
-  <si>
-    <t>Database_Image_Name</t>
-  </si>
-  <si>
-    <t>mcr.microsoft.com/mssql/server:2019-latest</t>
-  </si>
-  <si>
-    <t>Database_Container_Name</t>
-  </si>
-  <si>
-    <t>auto-grading-sqlserver</t>
-  </si>
-  <si>
-    <t>Database_Container_Internal_Port</t>
-  </si>
-  <si>
-    <t>Database_Container_Host_Port</t>
-  </si>
-  <si>
-    <t>Database_Username</t>
-  </si>
-  <si>
-    <t>sa</t>
-  </si>
-  <si>
-    <t>Database_Password</t>
-  </si>
-  <si>
-    <t>Khanh@2721</t>
-  </si>
-  <si>
-    <t>Default_Database_Name</t>
-  </si>
-  <si>
-    <t>PE_PRN_Sum25B5_WA</t>
-  </si>
-  <si>
-    <t>Default_Database_File_Path</t>
-  </si>
-  <si>
-    <t>Meta\database.sql</t>
-  </si>
-  <si>
-    <t>Runtimes_Folder</t>
-  </si>
-  <si>
-    <t>Meta\runtimes</t>
-  </si>
-  <si>
-    <t>ConnectDb_File</t>
-  </si>
-  <si>
-    <t>SignalR_Hub</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>create_network</t>
-  </si>
-  <si>
-    <t>create docker network</t>
-  </si>
-  <si>
-    <t>create_sqlserver_container</t>
-  </si>
-  <si>
-    <t>deploy sqlserver image as container</t>
-  </si>
-  <si>
-    <t>create_database_in_sqlserver</t>
-  </si>
-  <si>
-    <t>create database in sqlserver container, including copy sql file into container</t>
-  </si>
-  <si>
-    <t>build_solution_image</t>
-  </si>
-  <si>
-    <t>build solution image</t>
-  </si>
-  <si>
-    <t>create_solution_container</t>
-  </si>
-  <si>
-    <t>deploy solution image as container</t>
-  </si>
-  <si>
-    <t>Config Solution</t>
-  </si>
-  <si>
-    <t>modify_connection_string</t>
-  </si>
-  <si>
-    <t>Modify connection data in solution</t>
-  </si>
-  <si>
-    <t>override_file</t>
-  </si>
-  <si>
-    <t>replace_parts_from_files</t>
-  </si>
-  <si>
-    <t>validate_existence</t>
-  </si>
-  <si>
-    <t>validate_content</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Keyword action</t>
-  </si>
-  <si>
-    <t>copy_essential_files_and_folders</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="9">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Times"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="10"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -337,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -439,105 +243,179 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="2" applyAlignment="1">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="5" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="6" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="8" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="9" applyFill="1" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="9" applyFill="1" borderId="7" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="10" applyFill="1" borderId="8" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -857,347 +735,469 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="30.796875" customWidth="1" style="1"/>
-    <col min="2" max="2" width="42.8984375" customWidth="1" style="1"/>
-    <col min="3" max="3" bestFit="1" width="10.59765625" customWidth="1" style="1"/>
-    <col min="4" max="4" width="9.09765625" customWidth="1" style="1"/>
-    <col min="5" max="16384" width="9.09765625" customWidth="1" style="1"/>
+    <col width="30.796875" customWidth="1" style="1" min="1" max="1"/>
+    <col width="42.8984375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.09765625" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9.09765625" customWidth="1" style="1" min="5" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>3</v>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Environment_Type</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>dotnet</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="21.75" customHeight="1">
-      <c r="A3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>5</v>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Docker_Network</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>auto-grading-network</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>7</v>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Code_Image_Name</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>auto-grading-console:latest</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>9</v>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Code_Container_Name</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>auto-grading-dotnet-console-app</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Code_Container_Internal_Port</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="24">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Code_Container_Host_Port</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
         <v>8081</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>App_Type</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="10"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Given_Console_Container_Name</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="11"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Given_Console_File</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="11"/>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Given_Console_Internal_Port</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="12"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Given_Console_Host_Port</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>19</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Database_Image_Name</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>mcr.microsoft.com/mssql/server:2019-latest</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>21</v>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Database_Container_Name</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>auto-grading-sqlserver</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Database_Container_Internal_Port</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
         <v>1433</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Database_Container_Host_Port</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
         <v>1434</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Database_Username</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>27</v>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Database_Password</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Khanh@2721</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>29</v>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Default_Database_Name</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>PE_PRN_Sum25B5_WA</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>31</v>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Default_Database_File_Path</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Meta\database.sql</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>33</v>
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Runtimes_Folder</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Meta\runtimes</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="13"/>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>ConnectDb_File</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="15"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>SignalR_Hub</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B18" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A83C95-3B80-4231-A2A3-554283AC2A02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.59765625" customWidth="1" style="6"/>
-    <col min="2" max="2" width="37.19921875" customWidth="1" style="7"/>
-    <col min="3" max="3" width="66" customWidth="1"/>
+    <col width="21.59765625" customWidth="1" style="6" min="1" max="1"/>
+    <col width="37.19921875" customWidth="1" style="7" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>38</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>41</v>
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>create_network</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>create docker network</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>create_sqlserver_container</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>deploy sqlserver image as container</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18"/>
-      <c r="B4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>45</v>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>create_database_in_sqlserver</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>create database in sqlserver container, including copy sql file into container</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18"/>
-      <c r="B5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>build_solution_image</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>build solution image</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18"/>
-      <c r="B6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>create_solution_container</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>deploy solution image as container</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>52</v>
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Config Solution</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>modify_connection_string</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Modify connection data in solution</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18"/>
-      <c r="B8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>override_file</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18"/>
-      <c r="B9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="3"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>replace_parts_from_files</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>validate_existence</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20"/>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4"/>
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>validate_content</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
+    <mergeCell ref="A7:A11"/>
     <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A8B865-FC4E-42B9-9CDF-4A31D67503FE}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1" style="25"/>
-    <col min="2" max="2" bestFit="1" width="27.81640625" customWidth="1" style="25"/>
-    <col min="3" max="16384" width="8.90625" customWidth="1" style="25"/>
+    <col width="7" customWidth="1" style="25" min="1" max="1"/>
+    <col width="27.81640625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="8.90625" customWidth="1" style="25" min="3" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>58</v>
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Keyword action</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27">
+      <c r="A2" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>59</v>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>copy_essential_files_and_folders</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
+      <c r="A3" s="27" t="n"/>
+      <c r="B3" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>